--- a/362-assn-2/362-assn2-Truth Tables.xlsx
+++ b/362-assn-2/362-assn2-Truth Tables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thomr\OneDrive\Documents\5 - School\CS362-Software-Engineering-2\362-assn-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{060A5E14-C08B-4C60-B8CD-525AAD46F900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAE65389-2238-42C8-B5C6-91C82468C0EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{73352396-CEF2-46C0-A4DD-BEC691EFBD9E}"/>
   </bookViews>
@@ -194,7 +194,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -205,7 +205,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -213,11 +212,13 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -608,7 +609,7 @@
       <c r="E2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="10"/>
+      <c r="H2" s="22"/>
       <c r="I2" s="11"/>
       <c r="J2" s="11"/>
       <c r="K2" s="2"/>
@@ -618,10 +619,10 @@
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
-      <c r="R2" s="12"/>
-      <c r="S2" s="12"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
       <c r="T2" s="2"/>
-      <c r="U2" s="13"/>
+      <c r="U2" s="12"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3" s="7"/>
@@ -637,7 +638,7 @@
       <c r="E3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="14"/>
+      <c r="H3" s="21"/>
       <c r="I3" s="15"/>
       <c r="J3" s="3"/>
       <c r="K3" s="15"/>
@@ -647,10 +648,10 @@
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
-      <c r="R3" s="16"/>
-      <c r="S3" s="16"/>
+      <c r="R3" s="14"/>
+      <c r="S3" s="14"/>
       <c r="T3" s="3"/>
-      <c r="U3" s="17"/>
+      <c r="U3" s="16"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
@@ -668,9 +669,9 @@
       <c r="F4">
         <v>1</v>
       </c>
-      <c r="H4" s="14"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
@@ -678,10 +679,10 @@
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
-      <c r="R4" s="16"/>
-      <c r="S4" s="16"/>
+      <c r="R4" s="14"/>
+      <c r="S4" s="14"/>
       <c r="T4" s="3"/>
-      <c r="U4" s="17"/>
+      <c r="U4" s="16"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A5" s="4"/>
@@ -700,20 +701,20 @@
       <c r="F5">
         <v>10</v>
       </c>
-      <c r="H5" s="14"/>
-      <c r="I5" s="15"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="14"/>
       <c r="J5" s="3"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
-      <c r="R5" s="16"/>
-      <c r="S5" s="16"/>
+      <c r="R5" s="14"/>
+      <c r="S5" s="14"/>
       <c r="T5" s="3"/>
-      <c r="U5" s="17"/>
+      <c r="U5" s="16"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A6" s="8"/>
@@ -729,7 +730,7 @@
       <c r="E6" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="H6" s="14"/>
+      <c r="H6" s="21"/>
       <c r="I6" s="15"/>
       <c r="J6" s="3"/>
       <c r="K6" s="15"/>
@@ -741,8 +742,8 @@
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
-      <c r="T6" s="16"/>
-      <c r="U6" s="18"/>
+      <c r="T6" s="14"/>
+      <c r="U6" s="23"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7" s="8"/>
@@ -758,7 +759,7 @@
       <c r="E7" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="H7" s="14"/>
+      <c r="H7" s="21"/>
       <c r="I7" s="15"/>
       <c r="J7" s="3"/>
       <c r="K7" s="15"/>
@@ -770,8 +771,8 @@
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
-      <c r="T7" s="16"/>
-      <c r="U7" s="18"/>
+      <c r="T7" s="14"/>
+      <c r="U7" s="23"/>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
@@ -790,11 +791,11 @@
       <c r="F8">
         <v>0</v>
       </c>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="14"/>
       <c r="J8" s="3"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
@@ -802,8 +803,8 @@
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
-      <c r="T8" s="16"/>
-      <c r="U8" s="18"/>
+      <c r="T8" s="14"/>
+      <c r="U8" s="23"/>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A9" s="3"/>
@@ -822,11 +823,11 @@
       <c r="F9">
         <v>3</v>
       </c>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="14"/>
       <c r="J9" s="3"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
@@ -834,8 +835,8 @@
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
-      <c r="T9" s="16"/>
-      <c r="U9" s="18"/>
+      <c r="T9" s="14"/>
+      <c r="U9" s="23"/>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A10" s="9"/>
@@ -851,9 +852,9 @@
       <c r="E10" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
@@ -863,8 +864,8 @@
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
-      <c r="T10" s="16"/>
-      <c r="U10" s="18"/>
+      <c r="T10" s="14"/>
+      <c r="U10" s="23"/>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
@@ -883,11 +884,11 @@
       <c r="F11">
         <v>50</v>
       </c>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="14"/>
       <c r="J11" s="3"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
+      <c r="K11" s="14"/>
+      <c r="L11" s="14"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
@@ -895,8 +896,8 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-      <c r="T11" s="16"/>
-      <c r="U11" s="18"/>
+      <c r="T11" s="14"/>
+      <c r="U11" s="23"/>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A12" s="8"/>
@@ -912,7 +913,7 @@
       <c r="E12" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="H12" s="14"/>
+      <c r="H12" s="21"/>
       <c r="I12" s="15"/>
       <c r="J12" s="3"/>
       <c r="K12" s="15"/>
@@ -924,8 +925,8 @@
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
-      <c r="T12" s="16"/>
-      <c r="U12" s="18"/>
+      <c r="T12" s="14"/>
+      <c r="U12" s="23"/>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A13" s="4"/>
@@ -944,11 +945,11 @@
       <c r="F13">
         <v>25</v>
       </c>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="14"/>
       <c r="J13" s="3"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
@@ -956,8 +957,8 @@
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
-      <c r="T13" s="16"/>
-      <c r="U13" s="18"/>
+      <c r="T13" s="14"/>
+      <c r="U13" s="23"/>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
@@ -975,20 +976,20 @@
       <c r="F14">
         <v>15</v>
       </c>
-      <c r="H14" s="19"/>
+      <c r="H14" s="17"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="15"/>
+      <c r="M14" s="14"/>
+      <c r="N14" s="14"/>
       <c r="O14" s="3"/>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="15"/>
+      <c r="P14" s="14"/>
+      <c r="Q14" s="14"/>
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
-      <c r="T14" s="16"/>
-      <c r="U14" s="18"/>
+      <c r="T14" s="14"/>
+      <c r="U14" s="23"/>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
@@ -1006,20 +1007,20 @@
       <c r="F15">
         <v>39</v>
       </c>
-      <c r="H15" s="19"/>
+      <c r="H15" s="17"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="15"/>
-      <c r="O15" s="15"/>
+      <c r="M15" s="14"/>
+      <c r="N15" s="14"/>
+      <c r="O15" s="14"/>
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
       <c r="S15" s="3"/>
-      <c r="T15" s="16"/>
-      <c r="U15" s="18"/>
+      <c r="T15" s="14"/>
+      <c r="U15" s="23"/>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A16" s="7"/>
@@ -1035,7 +1036,7 @@
       <c r="E16" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="H16" s="19"/>
+      <c r="H16" s="17"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
@@ -1047,8 +1048,8 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-      <c r="T16" s="16"/>
-      <c r="U16" s="18"/>
+      <c r="T16" s="14"/>
+      <c r="U16" s="23"/>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A17" s="7"/>
@@ -1064,7 +1065,7 @@
       <c r="E17" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="H17" s="19"/>
+      <c r="H17" s="17"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
@@ -1076,11 +1077,11 @@
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
       <c r="S17" s="3"/>
-      <c r="T17" s="16"/>
-      <c r="U17" s="18"/>
+      <c r="T17" s="14"/>
+      <c r="U17" s="23"/>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="H18" s="20"/>
+      <c r="H18" s="18"/>
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
       <c r="K18" s="4"/>
@@ -1093,7 +1094,7 @@
       <c r="R18" s="4"/>
       <c r="S18" s="4"/>
       <c r="T18" s="4"/>
-      <c r="U18" s="21"/>
+      <c r="U18" s="19"/>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A21" s="7"/>
@@ -1102,7 +1103,7 @@
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A22" s="22"/>
+      <c r="A22" s="20"/>
       <c r="B22" t="s">
         <v>7</v>
       </c>
